--- a/PP25-26.xlsx
+++ b/PP25-26.xlsx
@@ -1,37 +1,73 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://noncurat-my.sharepoint.com/personal/noncurat_noncurat_onmicrosoft_com/Documents/Githubclones/Python_for_Excel-EOFY-EOFY26/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_2B59D2BFD3305E89B178C131557168736EC1FEC6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57B5D49C-73F8-4411-8CD4-ED71ED3DDD6D}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView minimized="1" xWindow="12735" yWindow="1230" windowWidth="13170" windowHeight="19290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="9">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Trans_Details</t>
+  </si>
+  <si>
+    <t>Trans_Dr</t>
+  </si>
+  <si>
+    <t>Trans_Cr</t>
+  </si>
+  <si>
+    <t>Amazon Online Purchase</t>
+  </si>
+  <si>
+    <t>Uber Eats Food Delivery</t>
+  </si>
+  <si>
+    <t>Ebay Purchase</t>
+  </si>
+  <si>
+    <t>Spotify Music Subscription</t>
+  </si>
+  <si>
+    <t>PayPal Payment Received</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -50,81 +86,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -412,313 +389,245 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Trans_Details</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Trans_Dr</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Trans_Cr</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>45840</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Amazon Online Purchase</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>89.99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>45844</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Uber Eats Food Delivery</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3">
         <v>45.5</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>45847</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Amazon Online Purchase</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4">
         <v>134.75</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>45852</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ebay Purchase</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5">
         <v>67.8</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>45857</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Uber Eats Food Delivery</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6">
         <v>38.9</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>45861</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Amazon Online Purchase</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7">
         <v>210</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>45867</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Spotify Music Subscription</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8">
         <v>9.99</v>
       </c>
-      <c r="D8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>45873</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ebay Purchase</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9">
         <v>54.2</v>
       </c>
-      <c r="D9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>45877</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Uber Eats Food Delivery</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10">
         <v>52.3</v>
       </c>
-      <c r="D10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>45882</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Amazon Online Purchase</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11">
         <v>178.45</v>
       </c>
-      <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>45886</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Spotify Music Subscription</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12">
         <v>9.99</v>
       </c>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>45890</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Ebay Purchase</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13">
         <v>43.6</v>
       </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>45895</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Amazon Online Purchase</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14">
         <v>95</v>
       </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>45901</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Uber Eats Food Delivery</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15">
         <v>61.75</v>
       </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>45906</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>PayPal Payment Received</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="n">
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16">
         <v>320</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>45910</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Amazon Online Purchase</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17">
         <v>145.9</v>
       </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>45914</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Spotify Music Subscription</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18">
         <v>9.99</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>45919</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Uber Eats Food Delivery</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19">
         <v>48.2</v>
       </c>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>45923</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Ebay Purchase</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20">
+        <v>72.400000000000006</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>45927</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>PayPal Payment Received</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="n">
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21">
         <v>185</v>
       </c>
     </row>
